--- a/data/state_total_area.xlsx
+++ b/data/state_total_area.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_MONASH_UNI\_Y3S1\FIT3179\DV2_repo\FIT3179_DV2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B50F6C-51C7-4C09-BFD6-1675E0B5D980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53D75C24-F732-4FF6-8EB8-C8112B6A289F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DDE188FF-7C21-46E8-8FCE-0CDF76BE4A64}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DDE188FF-7C21-46E8-8FCE-0CDF76BE4A64}"/>
   </bookViews>
   <sheets>
     <sheet name="Protected Land area" sheetId="2" r:id="rId1"/>
@@ -138,11 +138,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -634,10 +633,6 @@
       <c r="C2">
         <v>1021300</v>
       </c>
-      <c r="D2" t="b">
-        <f>IF(C2&gt;B2, TRUE, FALSE)</f>
-        <v>1</v>
-      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -649,10 +644,6 @@
       <c r="C3">
         <v>11574000</v>
       </c>
-      <c r="D3" t="b">
-        <f t="shared" ref="D3:D10" si="0">IF(C3&gt;B3, TRUE, FALSE)</f>
-        <v>1</v>
-      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -664,10 +655,6 @@
       <c r="C4">
         <v>6003200</v>
       </c>
-      <c r="D4" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -679,10 +666,6 @@
       <c r="C5">
         <v>880200</v>
       </c>
-      <c r="D5" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -694,10 +677,6 @@
       <c r="C6">
         <v>7456</v>
       </c>
-      <c r="D6" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -709,10 +688,6 @@
       <c r="C7">
         <v>2235700</v>
       </c>
-      <c r="D7" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -724,10 +699,6 @@
       <c r="C8">
         <v>12199400</v>
       </c>
-      <c r="D8" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -739,10 +710,6 @@
       <c r="C9">
         <v>7183900</v>
       </c>
-      <c r="D9" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -754,22 +721,9 @@
       <c r="C10">
         <v>852973361.39999998</v>
       </c>
-      <c r="D10" t="b">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J12" s="2"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J15" s="2"/>
+      <c r="J13" s="2"/>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B18" s="1"/>
